--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8808,6 +8808,121 @@
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>114799897</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57235</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Suddesjaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>685548</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7315601</v>
+      </c>
+      <c r="S79" t="n">
+        <v>50</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>barksprätt i gran</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -9889,10 +9889,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118642378</v>
+        <v>118640611</v>
       </c>
       <c r="B89" t="n">
-        <v>90749</v>
+        <v>77416</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9901,25 +9901,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>65</v>
+        <v>6487</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9929,13 +9929,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>685056</v>
+        <v>685210</v>
       </c>
       <c r="R89" t="n">
-        <v>7316028</v>
+        <v>7315857</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9979,12 +9979,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9995,10 +9995,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118640611</v>
+        <v>118642378</v>
       </c>
       <c r="B90" t="n">
-        <v>77416</v>
+        <v>90749</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10007,25 +10007,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6487</v>
+        <v>65</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10035,13 +10035,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>685210</v>
+        <v>685056</v>
       </c>
       <c r="R90" t="n">
-        <v>7315857</v>
+        <v>7316028</v>
       </c>
       <c r="S90" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10085,12 +10085,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10207,10 +10207,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118640590</v>
+        <v>118642374</v>
       </c>
       <c r="B92" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10223,21 +10223,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10247,13 +10247,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>685237</v>
+        <v>685042</v>
       </c>
       <c r="R92" t="n">
-        <v>7315783</v>
+        <v>7316013</v>
       </c>
       <c r="S92" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10297,12 +10297,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10313,10 +10313,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118642377</v>
+        <v>118640590</v>
       </c>
       <c r="B93" t="n">
-        <v>78221</v>
+        <v>79102</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10329,21 +10329,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10353,13 +10353,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>685147</v>
+        <v>685237</v>
       </c>
       <c r="R93" t="n">
-        <v>7315691</v>
+        <v>7315783</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10403,12 +10403,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10419,10 +10419,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118642374</v>
+        <v>118642377</v>
       </c>
       <c r="B94" t="n">
-        <v>79073</v>
+        <v>78221</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10435,21 +10435,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10459,10 +10459,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>685042</v>
+        <v>685147</v>
       </c>
       <c r="R94" t="n">
-        <v>7316013</v>
+        <v>7315691</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10737,10 +10737,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118640604</v>
+        <v>118640588</v>
       </c>
       <c r="B97" t="n">
-        <v>90749</v>
+        <v>74596</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10749,25 +10749,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>65</v>
+        <v>6440</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10777,10 +10777,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>685053</v>
+        <v>685142</v>
       </c>
       <c r="R97" t="n">
-        <v>7316028</v>
+        <v>7315652</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -10843,10 +10843,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118640588</v>
+        <v>118640604</v>
       </c>
       <c r="B98" t="n">
-        <v>74596</v>
+        <v>90749</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10855,25 +10855,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>65</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10883,10 +10883,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>685142</v>
+        <v>685053</v>
       </c>
       <c r="R98" t="n">
-        <v>7315652</v>
+        <v>7316028</v>
       </c>
       <c r="S98" t="n">
         <v>1</v>
@@ -11373,10 +11373,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118640600</v>
+        <v>118640440</v>
       </c>
       <c r="B103" t="n">
-        <v>78221</v>
+        <v>91779</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11385,38 +11385,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>685180</v>
+        <v>685191</v>
       </c>
       <c r="R103" t="n">
-        <v>7315662</v>
+        <v>7315970</v>
       </c>
       <c r="S103" t="n">
         <v>1</v>
@@ -11463,12 +11463,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11479,10 +11479,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118640440</v>
+        <v>118640591</v>
       </c>
       <c r="B104" t="n">
-        <v>91779</v>
+        <v>79102</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11491,38 +11491,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>685191</v>
+        <v>685079</v>
       </c>
       <c r="R104" t="n">
-        <v>7315970</v>
+        <v>7316003</v>
       </c>
       <c r="S104" t="n">
         <v>1</v>
@@ -11569,12 +11569,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11585,10 +11585,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118640591</v>
+        <v>118640600</v>
       </c>
       <c r="B105" t="n">
-        <v>79102</v>
+        <v>78221</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11601,21 +11601,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11625,10 +11625,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>685079</v>
+        <v>685180</v>
       </c>
       <c r="R105" t="n">
-        <v>7316003</v>
+        <v>7315662</v>
       </c>
       <c r="S105" t="n">
         <v>1</v>
@@ -12751,10 +12751,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118640785</v>
+        <v>118640781</v>
       </c>
       <c r="B116" t="n">
-        <v>78220</v>
+        <v>91795</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12767,21 +12767,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12791,10 +12791,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>685195</v>
+        <v>685168</v>
       </c>
       <c r="R116" t="n">
-        <v>7315739</v>
+        <v>7315680</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12835,7 +12835,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12858,10 +12857,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118640781</v>
+        <v>118640785</v>
       </c>
       <c r="B117" t="n">
-        <v>91795</v>
+        <v>78220</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12874,21 +12873,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12898,10 +12897,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>685168</v>
+        <v>685195</v>
       </c>
       <c r="R117" t="n">
-        <v>7315680</v>
+        <v>7315739</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12942,6 +12941,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13494,10 +13494,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118640776</v>
+        <v>118640790</v>
       </c>
       <c r="B123" t="n">
-        <v>79073</v>
+        <v>91779</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13506,25 +13506,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13534,10 +13534,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685197</v>
+        <v>685230</v>
       </c>
       <c r="R123" t="n">
-        <v>7315733</v>
+        <v>7315855</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13600,10 +13600,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118640790</v>
+        <v>118640776</v>
       </c>
       <c r="B124" t="n">
-        <v>91779</v>
+        <v>79073</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13612,25 +13612,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13640,10 +13640,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685230</v>
+        <v>685197</v>
       </c>
       <c r="R124" t="n">
-        <v>7315855</v>
+        <v>7315733</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14240,10 +14240,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118644451</v>
+        <v>118644440</v>
       </c>
       <c r="B130" t="n">
-        <v>78566</v>
+        <v>74596</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14256,21 +14256,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14280,10 +14280,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685148</v>
+        <v>685139</v>
       </c>
       <c r="R130" t="n">
-        <v>7315650</v>
+        <v>7315644</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -14346,10 +14346,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118644440</v>
+        <v>118644451</v>
       </c>
       <c r="B131" t="n">
-        <v>74596</v>
+        <v>78566</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14362,21 +14362,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14386,10 +14386,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685139</v>
+        <v>685148</v>
       </c>
       <c r="R131" t="n">
-        <v>7315644</v>
+        <v>7315650</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14982,10 +14982,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118644444</v>
+        <v>118644453</v>
       </c>
       <c r="B137" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14998,21 +14998,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15022,10 +15022,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685043</v>
+        <v>685164</v>
       </c>
       <c r="R137" t="n">
-        <v>7316017</v>
+        <v>7315966</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15088,10 +15088,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118644453</v>
+        <v>118644444</v>
       </c>
       <c r="B138" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15104,21 +15104,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15128,10 +15128,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685164</v>
+        <v>685043</v>
       </c>
       <c r="R138" t="n">
-        <v>7315966</v>
+        <v>7316017</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -12964,10 +12964,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118640788</v>
+        <v>118640773</v>
       </c>
       <c r="B118" t="n">
-        <v>90749</v>
+        <v>79102</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12976,25 +12976,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13004,10 +13004,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685048</v>
+        <v>685201</v>
       </c>
       <c r="R118" t="n">
-        <v>7316017</v>
+        <v>7315735</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13070,7 +13070,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118640773</v>
+        <v>118640774</v>
       </c>
       <c r="B119" t="n">
         <v>79102</v>
@@ -13110,10 +13110,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>685201</v>
+        <v>685022</v>
       </c>
       <c r="R119" t="n">
-        <v>7315735</v>
+        <v>7316004</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13176,10 +13176,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118640774</v>
+        <v>118640788</v>
       </c>
       <c r="B120" t="n">
-        <v>79102</v>
+        <v>90749</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13188,25 +13188,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13216,10 +13216,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685022</v>
+        <v>685048</v>
       </c>
       <c r="R120" t="n">
-        <v>7316004</v>
+        <v>7316017</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -9253,10 +9253,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118640601</v>
+        <v>118640606</v>
       </c>
       <c r="B83" t="n">
-        <v>78220</v>
+        <v>91779</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9265,25 +9265,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>685239</v>
+        <v>685216</v>
       </c>
       <c r="R83" t="n">
-        <v>7315772</v>
+        <v>7315926</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -9359,10 +9359,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118640610</v>
+        <v>118642377</v>
       </c>
       <c r="B84" t="n">
-        <v>77416</v>
+        <v>78221</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9375,21 +9375,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9399,13 +9399,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>685226</v>
+        <v>685147</v>
       </c>
       <c r="R84" t="n">
-        <v>7315821</v>
+        <v>7315691</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9449,12 +9449,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9465,10 +9465,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118640602</v>
+        <v>118640609</v>
       </c>
       <c r="B85" t="n">
-        <v>78566</v>
+        <v>91779</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9477,25 +9477,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9505,10 +9505,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>685142</v>
+        <v>685029</v>
       </c>
       <c r="R85" t="n">
-        <v>7315652</v>
+        <v>7316018</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -9571,7 +9571,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118642383</v>
+        <v>118640440</v>
       </c>
       <c r="B86" t="n">
         <v>91779</v>
@@ -9607,17 +9607,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>685019</v>
+        <v>685191</v>
       </c>
       <c r="R86" t="n">
-        <v>7316024</v>
+        <v>7315970</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9661,12 +9661,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9677,10 +9677,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118640609</v>
+        <v>118640604</v>
       </c>
       <c r="B87" t="n">
-        <v>91779</v>
+        <v>90749</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9689,25 +9689,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9717,10 +9717,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>685029</v>
+        <v>685053</v>
       </c>
       <c r="R87" t="n">
-        <v>7316018</v>
+        <v>7316028</v>
       </c>
       <c r="S87" t="n">
         <v>1</v>
@@ -9783,7 +9783,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118642384</v>
+        <v>118640611</v>
       </c>
       <c r="B88" t="n">
         <v>77416</v>
@@ -9823,13 +9823,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>685281</v>
+        <v>685210</v>
       </c>
       <c r="R88" t="n">
-        <v>7315800</v>
+        <v>7315857</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9873,12 +9873,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9889,10 +9889,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118640611</v>
+        <v>118640430</v>
       </c>
       <c r="B89" t="n">
-        <v>77416</v>
+        <v>79102</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9905,34 +9905,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>685210</v>
+        <v>685242</v>
       </c>
       <c r="R89" t="n">
-        <v>7315857</v>
+        <v>7315784</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
@@ -9979,12 +9979,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9995,10 +9995,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118642378</v>
+        <v>118640592</v>
       </c>
       <c r="B90" t="n">
-        <v>90749</v>
+        <v>79102</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10007,25 +10007,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10035,13 +10035,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>685056</v>
+        <v>685017</v>
       </c>
       <c r="R90" t="n">
-        <v>7316028</v>
+        <v>7316004</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10085,12 +10085,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10101,10 +10101,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118640595</v>
+        <v>118640588</v>
       </c>
       <c r="B91" t="n">
-        <v>79073</v>
+        <v>74596</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10117,21 +10117,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10141,10 +10141,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>685042</v>
+        <v>685142</v>
       </c>
       <c r="R91" t="n">
-        <v>7316018</v>
+        <v>7315652</v>
       </c>
       <c r="S91" t="n">
         <v>1</v>
@@ -10207,10 +10207,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118642374</v>
+        <v>118640602</v>
       </c>
       <c r="B92" t="n">
-        <v>79073</v>
+        <v>78566</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10223,21 +10223,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>864</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10247,13 +10247,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>685042</v>
+        <v>685142</v>
       </c>
       <c r="R92" t="n">
-        <v>7316013</v>
+        <v>7315652</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10297,12 +10297,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10313,10 +10313,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118640590</v>
+        <v>118642374</v>
       </c>
       <c r="B93" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10329,21 +10329,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10353,13 +10353,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>685237</v>
+        <v>685042</v>
       </c>
       <c r="R93" t="n">
-        <v>7315783</v>
+        <v>7316013</v>
       </c>
       <c r="S93" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10403,12 +10403,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10419,10 +10419,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118642377</v>
+        <v>118640594</v>
       </c>
       <c r="B94" t="n">
-        <v>78221</v>
+        <v>79073</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10435,21 +10435,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10459,13 +10459,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>685147</v>
+        <v>685213</v>
       </c>
       <c r="R94" t="n">
-        <v>7315691</v>
+        <v>7315728</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10509,12 +10509,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10525,10 +10525,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118640430</v>
+        <v>118640608</v>
       </c>
       <c r="B95" t="n">
-        <v>79102</v>
+        <v>91779</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10537,38 +10537,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>685242</v>
+        <v>685209</v>
       </c>
       <c r="R95" t="n">
-        <v>7315784</v>
+        <v>7315725</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
@@ -10615,12 +10615,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10631,7 +10631,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118640608</v>
+        <v>118642382</v>
       </c>
       <c r="B96" t="n">
         <v>91779</v>
@@ -10671,13 +10671,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>685209</v>
+        <v>685188</v>
       </c>
       <c r="R96" t="n">
-        <v>7315725</v>
+        <v>7315970</v>
       </c>
       <c r="S96" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10721,12 +10721,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10737,10 +10737,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118640588</v>
+        <v>118642384</v>
       </c>
       <c r="B97" t="n">
-        <v>74596</v>
+        <v>77416</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10753,21 +10753,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6440</v>
+        <v>6487</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10777,13 +10777,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>685142</v>
+        <v>685281</v>
       </c>
       <c r="R97" t="n">
-        <v>7315652</v>
+        <v>7315800</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10827,12 +10827,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10843,10 +10843,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118640604</v>
+        <v>118640432</v>
       </c>
       <c r="B98" t="n">
-        <v>90749</v>
+        <v>91795</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10855,38 +10855,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>65</v>
+        <v>2059</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>685053</v>
+        <v>685169</v>
       </c>
       <c r="R98" t="n">
-        <v>7316028</v>
+        <v>7315682</v>
       </c>
       <c r="S98" t="n">
         <v>1</v>
@@ -10933,12 +10933,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10949,10 +10949,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118642386</v>
+        <v>118640590</v>
       </c>
       <c r="B99" t="n">
-        <v>77416</v>
+        <v>79102</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10965,21 +10965,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>685239</v>
+        <v>685237</v>
       </c>
       <c r="R99" t="n">
-        <v>7315866</v>
+        <v>7315783</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11039,12 +11039,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11055,10 +11055,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118640438</v>
+        <v>118642378</v>
       </c>
       <c r="B100" t="n">
-        <v>91779</v>
+        <v>90749</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11067,41 +11067,41 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>685156</v>
+        <v>685056</v>
       </c>
       <c r="R100" t="n">
-        <v>7315676</v>
+        <v>7316028</v>
       </c>
       <c r="S100" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11145,12 +11145,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11161,7 +11161,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118640607</v>
+        <v>118640438</v>
       </c>
       <c r="B101" t="n">
         <v>91779</v>
@@ -11197,14 +11197,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
         <v>685156</v>
       </c>
       <c r="R101" t="n">
-        <v>7315668</v>
+        <v>7315676</v>
       </c>
       <c r="S101" t="n">
         <v>1</v>
@@ -11251,12 +11251,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11267,10 +11267,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118640612</v>
+        <v>118640437</v>
       </c>
       <c r="B102" t="n">
-        <v>77868</v>
+        <v>78484</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11283,34 +11283,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>685222</v>
+        <v>685190</v>
       </c>
       <c r="R102" t="n">
-        <v>7315868</v>
+        <v>7315965</v>
       </c>
       <c r="S102" t="n">
         <v>1</v>
@@ -11357,12 +11357,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11373,10 +11373,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118640440</v>
+        <v>118642386</v>
       </c>
       <c r="B103" t="n">
-        <v>91779</v>
+        <v>77416</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11385,41 +11385,41 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>685191</v>
+        <v>685239</v>
       </c>
       <c r="R103" t="n">
-        <v>7315970</v>
+        <v>7315866</v>
       </c>
       <c r="S103" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11463,12 +11463,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11479,10 +11479,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118640591</v>
+        <v>118640595</v>
       </c>
       <c r="B104" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11495,21 +11495,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11519,10 +11519,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>685079</v>
+        <v>685042</v>
       </c>
       <c r="R104" t="n">
-        <v>7316003</v>
+        <v>7316018</v>
       </c>
       <c r="S104" t="n">
         <v>1</v>
@@ -11585,10 +11585,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118640600</v>
+        <v>118640612</v>
       </c>
       <c r="B105" t="n">
-        <v>78221</v>
+        <v>77868</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11601,21 +11601,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11625,10 +11625,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>685180</v>
+        <v>685222</v>
       </c>
       <c r="R105" t="n">
-        <v>7315662</v>
+        <v>7315868</v>
       </c>
       <c r="S105" t="n">
         <v>1</v>
@@ -11691,10 +11691,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118640432</v>
+        <v>118640591</v>
       </c>
       <c r="B106" t="n">
-        <v>91795</v>
+        <v>79102</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11707,34 +11707,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>685169</v>
+        <v>685079</v>
       </c>
       <c r="R106" t="n">
-        <v>7315682</v>
+        <v>7316003</v>
       </c>
       <c r="S106" t="n">
         <v>1</v>
@@ -11781,12 +11781,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11797,7 +11797,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118640606</v>
+        <v>118642383</v>
       </c>
       <c r="B107" t="n">
         <v>91779</v>
@@ -11837,13 +11837,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>685216</v>
+        <v>685019</v>
       </c>
       <c r="R107" t="n">
-        <v>7315926</v>
+        <v>7316024</v>
       </c>
       <c r="S107" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11887,12 +11887,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11903,10 +11903,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118640437</v>
+        <v>118640601</v>
       </c>
       <c r="B108" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11919,34 +11919,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>685190</v>
+        <v>685239</v>
       </c>
       <c r="R108" t="n">
-        <v>7315965</v>
+        <v>7315772</v>
       </c>
       <c r="S108" t="n">
         <v>1</v>
@@ -11993,12 +11993,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -12009,10 +12009,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118640592</v>
+        <v>118640607</v>
       </c>
       <c r="B109" t="n">
-        <v>79102</v>
+        <v>91779</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12021,25 +12021,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12049,10 +12049,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>685017</v>
+        <v>685156</v>
       </c>
       <c r="R109" t="n">
-        <v>7316004</v>
+        <v>7315668</v>
       </c>
       <c r="S109" t="n">
         <v>1</v>
@@ -12115,10 +12115,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118640594</v>
+        <v>118640610</v>
       </c>
       <c r="B110" t="n">
-        <v>79073</v>
+        <v>77416</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12131,21 +12131,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12155,10 +12155,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>685213</v>
+        <v>685226</v>
       </c>
       <c r="R110" t="n">
-        <v>7315728</v>
+        <v>7315821</v>
       </c>
       <c r="S110" t="n">
         <v>1</v>
@@ -12221,10 +12221,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118642382</v>
+        <v>118640600</v>
       </c>
       <c r="B111" t="n">
-        <v>91779</v>
+        <v>78221</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12233,25 +12233,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>685188</v>
+        <v>685180</v>
       </c>
       <c r="R111" t="n">
-        <v>7315970</v>
+        <v>7315662</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12311,12 +12311,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12433,10 +12433,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118661409</v>
+        <v>118640776</v>
       </c>
       <c r="B113" t="n">
-        <v>91779</v>
+        <v>79073</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12445,38 +12445,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjsure, Pi lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>685192</v>
+        <v>685197</v>
       </c>
       <c r="R113" t="n">
-        <v>7315652</v>
+        <v>7315733</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12523,12 +12523,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12539,7 +12539,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118640791</v>
+        <v>118661409</v>
       </c>
       <c r="B114" t="n">
         <v>91779</v>
@@ -12575,14 +12575,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Suddesjsure, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>685240</v>
+        <v>685192</v>
       </c>
       <c r="R114" t="n">
-        <v>7315893</v>
+        <v>7315652</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12629,12 +12629,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12645,10 +12645,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118640784</v>
+        <v>118640774</v>
       </c>
       <c r="B115" t="n">
-        <v>80441</v>
+        <v>79102</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12661,21 +12661,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12685,10 +12685,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>685196</v>
+        <v>685022</v>
       </c>
       <c r="R115" t="n">
-        <v>7315737</v>
+        <v>7316004</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12751,10 +12751,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118640781</v>
+        <v>118640791</v>
       </c>
       <c r="B116" t="n">
-        <v>91795</v>
+        <v>91779</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12763,25 +12763,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12791,10 +12791,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>685168</v>
+        <v>685240</v>
       </c>
       <c r="R116" t="n">
-        <v>7315680</v>
+        <v>7315893</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12857,10 +12857,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118640785</v>
+        <v>118640773</v>
       </c>
       <c r="B117" t="n">
-        <v>78220</v>
+        <v>79102</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12873,21 +12873,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12897,10 +12897,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>685195</v>
+        <v>685201</v>
       </c>
       <c r="R117" t="n">
-        <v>7315739</v>
+        <v>7315735</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12941,7 +12941,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12964,10 +12963,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118640773</v>
+        <v>118640784</v>
       </c>
       <c r="B118" t="n">
-        <v>79102</v>
+        <v>80441</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12980,21 +12979,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13004,10 +13003,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685201</v>
+        <v>685196</v>
       </c>
       <c r="R118" t="n">
-        <v>7315735</v>
+        <v>7315737</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13070,10 +13069,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118640774</v>
+        <v>118640792</v>
       </c>
       <c r="B119" t="n">
-        <v>79102</v>
+        <v>91779</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13082,25 +13081,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13110,10 +13109,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>685022</v>
+        <v>685179</v>
       </c>
       <c r="R119" t="n">
-        <v>7316004</v>
+        <v>7315961</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13176,10 +13175,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118640788</v>
+        <v>118640785</v>
       </c>
       <c r="B120" t="n">
-        <v>90749</v>
+        <v>78220</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13188,25 +13187,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13216,10 +13215,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685048</v>
+        <v>685195</v>
       </c>
       <c r="R120" t="n">
-        <v>7316017</v>
+        <v>7315739</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13260,6 +13259,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13282,10 +13282,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118640778</v>
+        <v>118640781</v>
       </c>
       <c r="B121" t="n">
-        <v>91783</v>
+        <v>91795</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13294,25 +13294,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4365</v>
+        <v>2059</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685199</v>
+        <v>685168</v>
       </c>
       <c r="R121" t="n">
-        <v>7315633</v>
+        <v>7315680</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13388,10 +13388,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118640775</v>
+        <v>118640788</v>
       </c>
       <c r="B122" t="n">
-        <v>79073</v>
+        <v>90749</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13400,25 +13400,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13428,10 +13428,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>685170</v>
+        <v>685048</v>
       </c>
       <c r="R122" t="n">
-        <v>7315649</v>
+        <v>7316017</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13494,10 +13494,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118640790</v>
+        <v>118640775</v>
       </c>
       <c r="B123" t="n">
-        <v>91779</v>
+        <v>79073</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13506,25 +13506,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13534,10 +13534,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685230</v>
+        <v>685170</v>
       </c>
       <c r="R123" t="n">
-        <v>7315855</v>
+        <v>7315649</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13600,10 +13600,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118640776</v>
+        <v>118640778</v>
       </c>
       <c r="B124" t="n">
-        <v>79073</v>
+        <v>91783</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13612,25 +13612,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229821</v>
+        <v>4365</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13640,10 +13640,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685197</v>
+        <v>685199</v>
       </c>
       <c r="R124" t="n">
-        <v>7315733</v>
+        <v>7315633</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13706,7 +13706,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118640792</v>
+        <v>118640790</v>
       </c>
       <c r="B125" t="n">
         <v>91779</v>
@@ -13746,10 +13746,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685179</v>
+        <v>685230</v>
       </c>
       <c r="R125" t="n">
-        <v>7315961</v>
+        <v>7315855</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13812,10 +13812,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118644454</v>
+        <v>118644457</v>
       </c>
       <c r="B126" t="n">
-        <v>90749</v>
+        <v>77416</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13824,25 +13824,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>65</v>
+        <v>6487</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13852,10 +13852,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685052</v>
+        <v>685225</v>
       </c>
       <c r="R126" t="n">
-        <v>7316025</v>
+        <v>7315875</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -14024,10 +14024,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118644458</v>
+        <v>118640783</v>
       </c>
       <c r="B128" t="n">
-        <v>77868</v>
+        <v>78221</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14040,37 +14040,40 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjsure, Pi lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685225</v>
+        <v>685195</v>
       </c>
       <c r="R128" t="n">
-        <v>7315875</v>
+        <v>7315735</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14108,18 +14111,19 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -14130,10 +14134,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118640783</v>
+        <v>118644454</v>
       </c>
       <c r="B129" t="n">
-        <v>78221</v>
+        <v>90749</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14142,44 +14146,41 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Suddesjsure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685195</v>
+        <v>685052</v>
       </c>
       <c r="R129" t="n">
-        <v>7315735</v>
+        <v>7316025</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14217,19 +14218,18 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14240,10 +14240,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118644440</v>
+        <v>118644456</v>
       </c>
       <c r="B130" t="n">
-        <v>74596</v>
+        <v>91779</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14252,25 +14252,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14280,10 +14280,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685139</v>
+        <v>685013</v>
       </c>
       <c r="R130" t="n">
-        <v>7315644</v>
+        <v>7316010</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -14346,10 +14346,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118644451</v>
+        <v>118644448</v>
       </c>
       <c r="B131" t="n">
-        <v>78566</v>
+        <v>91783</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14358,25 +14358,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>864</v>
+        <v>4365</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14386,10 +14386,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685148</v>
+        <v>685200</v>
       </c>
       <c r="R131" t="n">
-        <v>7315650</v>
+        <v>7315632</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14452,10 +14452,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118644456</v>
+        <v>118644455</v>
       </c>
       <c r="B132" t="n">
-        <v>91779</v>
+        <v>78129</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14464,25 +14464,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14492,10 +14492,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685013</v>
+        <v>685162</v>
       </c>
       <c r="R132" t="n">
-        <v>7316010</v>
+        <v>7315661</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14558,10 +14558,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118644443</v>
+        <v>118644445</v>
       </c>
       <c r="B133" t="n">
-        <v>79102</v>
+        <v>56502</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14570,38 +14570,46 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685022</v>
+        <v>685198</v>
       </c>
       <c r="R133" t="n">
-        <v>7316011</v>
+        <v>7315723</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -14634,6 +14642,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14664,10 +14677,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118644457</v>
+        <v>118644449</v>
       </c>
       <c r="B134" t="n">
-        <v>77416</v>
+        <v>91795</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14680,21 +14693,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6487</v>
+        <v>2059</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14704,10 +14717,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685225</v>
+        <v>685163</v>
       </c>
       <c r="R134" t="n">
-        <v>7315875</v>
+        <v>7315675</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -14770,10 +14783,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118644455</v>
+        <v>118644458</v>
       </c>
       <c r="B135" t="n">
-        <v>78129</v>
+        <v>77868</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14786,21 +14799,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14810,10 +14823,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685162</v>
+        <v>685225</v>
       </c>
       <c r="R135" t="n">
-        <v>7315661</v>
+        <v>7315875</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14876,10 +14889,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118644448</v>
+        <v>118644451</v>
       </c>
       <c r="B136" t="n">
-        <v>91783</v>
+        <v>78566</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14888,25 +14901,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4365</v>
+        <v>864</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14916,10 +14929,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685200</v>
+        <v>685148</v>
       </c>
       <c r="R136" t="n">
-        <v>7315632</v>
+        <v>7315650</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15194,10 +15207,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118644449</v>
+        <v>118644443</v>
       </c>
       <c r="B139" t="n">
-        <v>91795</v>
+        <v>79102</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15210,21 +15223,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15234,10 +15247,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685163</v>
+        <v>685022</v>
       </c>
       <c r="R139" t="n">
-        <v>7315675</v>
+        <v>7316011</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15300,10 +15313,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118644445</v>
+        <v>118644440</v>
       </c>
       <c r="B140" t="n">
-        <v>56502</v>
+        <v>74596</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15312,46 +15325,38 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685198</v>
+        <v>685139</v>
       </c>
       <c r="R140" t="n">
-        <v>7315723</v>
+        <v>7315644</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -15384,11 +15389,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD140" t="b">

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -10631,10 +10631,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118642382</v>
+        <v>118640432</v>
       </c>
       <c r="B96" t="n">
-        <v>91779</v>
+        <v>91795</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10643,41 +10643,41 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>685188</v>
+        <v>685169</v>
       </c>
       <c r="R96" t="n">
-        <v>7315970</v>
+        <v>7315682</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10721,12 +10721,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10737,10 +10737,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118642384</v>
+        <v>118642382</v>
       </c>
       <c r="B97" t="n">
-        <v>77416</v>
+        <v>91779</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10749,25 +10749,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10777,10 +10777,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>685281</v>
+        <v>685188</v>
       </c>
       <c r="R97" t="n">
-        <v>7315800</v>
+        <v>7315970</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10843,10 +10843,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118640432</v>
+        <v>118642384</v>
       </c>
       <c r="B98" t="n">
-        <v>91795</v>
+        <v>77416</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10859,37 +10859,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2059</v>
+        <v>6487</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>685169</v>
+        <v>685281</v>
       </c>
       <c r="R98" t="n">
-        <v>7315682</v>
+        <v>7315800</v>
       </c>
       <c r="S98" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10933,12 +10933,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11797,10 +11797,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118642383</v>
+        <v>118640601</v>
       </c>
       <c r="B107" t="n">
-        <v>91779</v>
+        <v>78220</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11809,25 +11809,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11837,13 +11837,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>685019</v>
+        <v>685239</v>
       </c>
       <c r="R107" t="n">
-        <v>7316024</v>
+        <v>7315772</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11887,12 +11887,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11903,10 +11903,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118640601</v>
+        <v>118642383</v>
       </c>
       <c r="B108" t="n">
-        <v>78220</v>
+        <v>91779</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11915,25 +11915,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11943,13 +11943,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>685239</v>
+        <v>685019</v>
       </c>
       <c r="R108" t="n">
-        <v>7315772</v>
+        <v>7316024</v>
       </c>
       <c r="S108" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11993,12 +11993,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -12009,10 +12009,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118640607</v>
+        <v>118640610</v>
       </c>
       <c r="B109" t="n">
-        <v>91779</v>
+        <v>77416</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12021,25 +12021,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12049,10 +12049,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>685156</v>
+        <v>685226</v>
       </c>
       <c r="R109" t="n">
-        <v>7315668</v>
+        <v>7315821</v>
       </c>
       <c r="S109" t="n">
         <v>1</v>
@@ -12115,10 +12115,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118640610</v>
+        <v>118640600</v>
       </c>
       <c r="B110" t="n">
-        <v>77416</v>
+        <v>78221</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12131,21 +12131,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12155,10 +12155,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>685226</v>
+        <v>685180</v>
       </c>
       <c r="R110" t="n">
-        <v>7315821</v>
+        <v>7315662</v>
       </c>
       <c r="S110" t="n">
         <v>1</v>
@@ -12221,10 +12221,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118640600</v>
+        <v>118640607</v>
       </c>
       <c r="B111" t="n">
-        <v>78221</v>
+        <v>91779</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12233,25 +12233,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12261,10 +12261,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>685180</v>
+        <v>685156</v>
       </c>
       <c r="R111" t="n">
-        <v>7315662</v>
+        <v>7315668</v>
       </c>
       <c r="S111" t="n">
         <v>1</v>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -9253,7 +9253,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118640606</v>
+        <v>118642382</v>
       </c>
       <c r="B83" t="n">
         <v>91779</v>
@@ -9293,13 +9293,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>685216</v>
+        <v>685188</v>
       </c>
       <c r="R83" t="n">
-        <v>7315926</v>
+        <v>7315970</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9343,12 +9343,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9359,10 +9359,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118642377</v>
+        <v>118642383</v>
       </c>
       <c r="B84" t="n">
-        <v>78221</v>
+        <v>91779</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9371,25 +9371,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9399,10 +9399,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>685147</v>
+        <v>685019</v>
       </c>
       <c r="R84" t="n">
-        <v>7315691</v>
+        <v>7316024</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9465,10 +9465,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118640609</v>
+        <v>118640432</v>
       </c>
       <c r="B85" t="n">
-        <v>91779</v>
+        <v>91795</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9477,38 +9477,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>685029</v>
+        <v>685169</v>
       </c>
       <c r="R85" t="n">
-        <v>7316018</v>
+        <v>7315682</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -9555,12 +9555,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9571,10 +9571,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118640440</v>
+        <v>118640610</v>
       </c>
       <c r="B86" t="n">
-        <v>91779</v>
+        <v>77416</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9583,38 +9583,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>685191</v>
+        <v>685226</v>
       </c>
       <c r="R86" t="n">
-        <v>7315970</v>
+        <v>7315821</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
@@ -9661,12 +9661,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9677,10 +9677,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118640604</v>
+        <v>118640595</v>
       </c>
       <c r="B87" t="n">
-        <v>90749</v>
+        <v>79073</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9689,25 +9689,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9717,10 +9717,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>685053</v>
+        <v>685042</v>
       </c>
       <c r="R87" t="n">
-        <v>7316028</v>
+        <v>7316018</v>
       </c>
       <c r="S87" t="n">
         <v>1</v>
@@ -9783,10 +9783,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118640611</v>
+        <v>118640592</v>
       </c>
       <c r="B88" t="n">
-        <v>77416</v>
+        <v>79102</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9799,21 +9799,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>685210</v>
+        <v>685017</v>
       </c>
       <c r="R88" t="n">
-        <v>7315857</v>
+        <v>7316004</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
@@ -9889,7 +9889,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118640430</v>
+        <v>118640591</v>
       </c>
       <c r="B89" t="n">
         <v>79102</v>
@@ -9925,14 +9925,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>685242</v>
+        <v>685079</v>
       </c>
       <c r="R89" t="n">
-        <v>7315784</v>
+        <v>7316003</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
@@ -9979,12 +9979,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9995,10 +9995,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118640592</v>
+        <v>118640594</v>
       </c>
       <c r="B90" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10011,21 +10011,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10035,10 +10035,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>685017</v>
+        <v>685213</v>
       </c>
       <c r="R90" t="n">
-        <v>7316004</v>
+        <v>7315728</v>
       </c>
       <c r="S90" t="n">
         <v>1</v>
@@ -10207,10 +10207,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118640602</v>
+        <v>118640438</v>
       </c>
       <c r="B92" t="n">
-        <v>78566</v>
+        <v>91779</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10219,38 +10219,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>685142</v>
+        <v>685156</v>
       </c>
       <c r="R92" t="n">
-        <v>7315652</v>
+        <v>7315676</v>
       </c>
       <c r="S92" t="n">
         <v>1</v>
@@ -10297,12 +10297,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10313,10 +10313,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118642374</v>
+        <v>118640437</v>
       </c>
       <c r="B93" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10329,37 +10329,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>685042</v>
+        <v>685190</v>
       </c>
       <c r="R93" t="n">
-        <v>7316013</v>
+        <v>7315965</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10403,12 +10403,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10419,7 +10419,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118640594</v>
+        <v>118642374</v>
       </c>
       <c r="B94" t="n">
         <v>79073</v>
@@ -10459,13 +10459,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>685213</v>
+        <v>685042</v>
       </c>
       <c r="R94" t="n">
-        <v>7315728</v>
+        <v>7316013</v>
       </c>
       <c r="S94" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10509,12 +10509,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10525,10 +10525,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118640608</v>
+        <v>118640604</v>
       </c>
       <c r="B95" t="n">
-        <v>91779</v>
+        <v>90749</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10537,25 +10537,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10565,10 +10565,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>685209</v>
+        <v>685053</v>
       </c>
       <c r="R95" t="n">
-        <v>7315725</v>
+        <v>7316028</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
@@ -10631,10 +10631,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118640432</v>
+        <v>118640440</v>
       </c>
       <c r="B96" t="n">
-        <v>91795</v>
+        <v>91779</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10643,25 +10643,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>685169</v>
+        <v>685191</v>
       </c>
       <c r="R96" t="n">
-        <v>7315682</v>
+        <v>7315970</v>
       </c>
       <c r="S96" t="n">
         <v>1</v>
@@ -10737,10 +10737,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118642382</v>
+        <v>118640430</v>
       </c>
       <c r="B97" t="n">
-        <v>91779</v>
+        <v>79102</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10749,41 +10749,41 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>685188</v>
+        <v>685242</v>
       </c>
       <c r="R97" t="n">
-        <v>7315970</v>
+        <v>7315784</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10827,12 +10827,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10843,10 +10843,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118642384</v>
+        <v>118640601</v>
       </c>
       <c r="B98" t="n">
-        <v>77416</v>
+        <v>78220</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10859,21 +10859,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10883,13 +10883,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>685281</v>
+        <v>685239</v>
       </c>
       <c r="R98" t="n">
-        <v>7315800</v>
+        <v>7315772</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10933,12 +10933,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10949,10 +10949,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118640590</v>
+        <v>118642386</v>
       </c>
       <c r="B99" t="n">
-        <v>79102</v>
+        <v>77416</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10965,21 +10965,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>685237</v>
+        <v>685239</v>
       </c>
       <c r="R99" t="n">
-        <v>7315783</v>
+        <v>7315866</v>
       </c>
       <c r="S99" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11039,12 +11039,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11055,10 +11055,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118642378</v>
+        <v>118640606</v>
       </c>
       <c r="B100" t="n">
-        <v>90749</v>
+        <v>91779</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11067,25 +11067,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11095,13 +11095,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>685056</v>
+        <v>685216</v>
       </c>
       <c r="R100" t="n">
-        <v>7316028</v>
+        <v>7315926</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11145,12 +11145,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11161,10 +11161,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118640438</v>
+        <v>118642378</v>
       </c>
       <c r="B101" t="n">
-        <v>91779</v>
+        <v>90749</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11173,41 +11173,41 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>685156</v>
+        <v>685056</v>
       </c>
       <c r="R101" t="n">
-        <v>7315676</v>
+        <v>7316028</v>
       </c>
       <c r="S101" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11251,12 +11251,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11267,10 +11267,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118640437</v>
+        <v>118642384</v>
       </c>
       <c r="B102" t="n">
-        <v>78484</v>
+        <v>77416</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11283,37 +11283,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>685190</v>
+        <v>685281</v>
       </c>
       <c r="R102" t="n">
-        <v>7315965</v>
+        <v>7315800</v>
       </c>
       <c r="S102" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11357,12 +11357,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11373,10 +11373,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118642386</v>
+        <v>118640590</v>
       </c>
       <c r="B103" t="n">
-        <v>77416</v>
+        <v>79102</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11389,21 +11389,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11413,13 +11413,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>685239</v>
+        <v>685237</v>
       </c>
       <c r="R103" t="n">
-        <v>7315866</v>
+        <v>7315783</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11463,12 +11463,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11479,10 +11479,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118640595</v>
+        <v>118640611</v>
       </c>
       <c r="B104" t="n">
-        <v>79073</v>
+        <v>77416</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11495,21 +11495,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11519,10 +11519,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>685042</v>
+        <v>685210</v>
       </c>
       <c r="R104" t="n">
-        <v>7316018</v>
+        <v>7315857</v>
       </c>
       <c r="S104" t="n">
         <v>1</v>
@@ -11691,10 +11691,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118640591</v>
+        <v>118640609</v>
       </c>
       <c r="B106" t="n">
-        <v>79102</v>
+        <v>91779</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11703,25 +11703,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11731,10 +11731,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>685079</v>
+        <v>685029</v>
       </c>
       <c r="R106" t="n">
-        <v>7316003</v>
+        <v>7316018</v>
       </c>
       <c r="S106" t="n">
         <v>1</v>
@@ -11797,10 +11797,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118640601</v>
+        <v>118640602</v>
       </c>
       <c r="B107" t="n">
-        <v>78220</v>
+        <v>78566</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11813,21 +11813,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>864</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11837,10 +11837,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>685239</v>
+        <v>685142</v>
       </c>
       <c r="R107" t="n">
-        <v>7315772</v>
+        <v>7315652</v>
       </c>
       <c r="S107" t="n">
         <v>1</v>
@@ -11903,7 +11903,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118642383</v>
+        <v>118640608</v>
       </c>
       <c r="B108" t="n">
         <v>91779</v>
@@ -11943,13 +11943,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>685019</v>
+        <v>685209</v>
       </c>
       <c r="R108" t="n">
-        <v>7316024</v>
+        <v>7315725</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11993,12 +11993,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -12009,10 +12009,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118640610</v>
+        <v>118640607</v>
       </c>
       <c r="B109" t="n">
-        <v>77416</v>
+        <v>91779</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12021,25 +12021,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12049,10 +12049,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>685226</v>
+        <v>685156</v>
       </c>
       <c r="R109" t="n">
-        <v>7315821</v>
+        <v>7315668</v>
       </c>
       <c r="S109" t="n">
         <v>1</v>
@@ -12221,10 +12221,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118640607</v>
+        <v>118642377</v>
       </c>
       <c r="B111" t="n">
-        <v>91779</v>
+        <v>78221</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12233,25 +12233,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>685156</v>
+        <v>685147</v>
       </c>
       <c r="R111" t="n">
-        <v>7315668</v>
+        <v>7315691</v>
       </c>
       <c r="S111" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12311,12 +12311,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12327,7 +12327,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118661410</v>
+        <v>118640790</v>
       </c>
       <c r="B112" t="n">
         <v>91779</v>
@@ -12363,14 +12363,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjsure, Pi lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>685231</v>
+        <v>685230</v>
       </c>
       <c r="R112" t="n">
-        <v>7315731</v>
+        <v>7315855</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12417,12 +12417,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12433,10 +12433,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118640776</v>
+        <v>118640791</v>
       </c>
       <c r="B113" t="n">
-        <v>79073</v>
+        <v>91779</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12445,25 +12445,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12473,10 +12473,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>685197</v>
+        <v>685240</v>
       </c>
       <c r="R113" t="n">
-        <v>7315733</v>
+        <v>7315893</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12539,10 +12539,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118661409</v>
+        <v>118640781</v>
       </c>
       <c r="B114" t="n">
-        <v>91779</v>
+        <v>91795</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12551,38 +12551,38 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjsure, Pi lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>685192</v>
+        <v>685168</v>
       </c>
       <c r="R114" t="n">
-        <v>7315652</v>
+        <v>7315680</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12629,12 +12629,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12751,10 +12751,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118640791</v>
+        <v>118640788</v>
       </c>
       <c r="B116" t="n">
-        <v>91779</v>
+        <v>90749</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12763,25 +12763,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12791,10 +12791,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>685240</v>
+        <v>685048</v>
       </c>
       <c r="R116" t="n">
-        <v>7315893</v>
+        <v>7316017</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12963,10 +12963,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118640784</v>
+        <v>118640785</v>
       </c>
       <c r="B118" t="n">
-        <v>80441</v>
+        <v>78220</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12979,21 +12979,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13003,10 +13003,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685196</v>
+        <v>685195</v>
       </c>
       <c r="R118" t="n">
-        <v>7315737</v>
+        <v>7315739</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13047,6 +13047,7 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13069,10 +13070,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118640792</v>
+        <v>118640776</v>
       </c>
       <c r="B119" t="n">
-        <v>91779</v>
+        <v>79073</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13081,25 +13082,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13109,10 +13110,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>685179</v>
+        <v>685197</v>
       </c>
       <c r="R119" t="n">
-        <v>7315961</v>
+        <v>7315733</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13175,10 +13176,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118640785</v>
+        <v>118640784</v>
       </c>
       <c r="B120" t="n">
-        <v>78220</v>
+        <v>80441</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13191,21 +13192,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13215,10 +13216,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685195</v>
+        <v>685196</v>
       </c>
       <c r="R120" t="n">
-        <v>7315739</v>
+        <v>7315737</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13259,7 +13260,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13282,10 +13282,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118640781</v>
+        <v>118661409</v>
       </c>
       <c r="B121" t="n">
-        <v>91795</v>
+        <v>91779</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13294,38 +13294,38 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Suddesjsure, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685168</v>
+        <v>685192</v>
       </c>
       <c r="R121" t="n">
-        <v>7315680</v>
+        <v>7315652</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13372,12 +13372,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13388,10 +13388,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118640788</v>
+        <v>118640775</v>
       </c>
       <c r="B122" t="n">
-        <v>90749</v>
+        <v>79073</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13400,25 +13400,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13428,10 +13428,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>685048</v>
+        <v>685170</v>
       </c>
       <c r="R122" t="n">
-        <v>7316017</v>
+        <v>7315649</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13494,10 +13494,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118640775</v>
+        <v>118661410</v>
       </c>
       <c r="B123" t="n">
-        <v>79073</v>
+        <v>91779</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13506,38 +13506,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Suddesjsure, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685170</v>
+        <v>685231</v>
       </c>
       <c r="R123" t="n">
-        <v>7315649</v>
+        <v>7315731</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13584,12 +13584,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13600,10 +13600,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118640778</v>
+        <v>118640792</v>
       </c>
       <c r="B124" t="n">
-        <v>91783</v>
+        <v>91779</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13612,25 +13612,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13640,10 +13640,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685199</v>
+        <v>685179</v>
       </c>
       <c r="R124" t="n">
-        <v>7315633</v>
+        <v>7315961</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13706,10 +13706,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118640790</v>
+        <v>118640778</v>
       </c>
       <c r="B125" t="n">
-        <v>91779</v>
+        <v>91783</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13718,25 +13718,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13746,10 +13746,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685230</v>
+        <v>685199</v>
       </c>
       <c r="R125" t="n">
-        <v>7315855</v>
+        <v>7315633</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13812,10 +13812,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118644457</v>
+        <v>118644456</v>
       </c>
       <c r="B126" t="n">
-        <v>77416</v>
+        <v>91779</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13824,25 +13824,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13852,10 +13852,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685225</v>
+        <v>685013</v>
       </c>
       <c r="R126" t="n">
-        <v>7315875</v>
+        <v>7316010</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -14024,10 +14024,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118640783</v>
+        <v>118644448</v>
       </c>
       <c r="B128" t="n">
-        <v>78221</v>
+        <v>91783</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14036,44 +14036,41 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>4365</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Suddesjsure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685195</v>
+        <v>685200</v>
       </c>
       <c r="R128" t="n">
-        <v>7315735</v>
+        <v>7315632</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14111,19 +14108,18 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -14134,10 +14130,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118644454</v>
+        <v>118640783</v>
       </c>
       <c r="B129" t="n">
-        <v>90749</v>
+        <v>78221</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14146,41 +14142,44 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjsure, Pi lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685052</v>
+        <v>685195</v>
       </c>
       <c r="R129" t="n">
-        <v>7316025</v>
+        <v>7315735</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14218,18 +14217,19 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14240,10 +14240,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118644456</v>
+        <v>118644444</v>
       </c>
       <c r="B130" t="n">
-        <v>91779</v>
+        <v>79073</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14252,25 +14252,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14280,10 +14280,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685013</v>
+        <v>685043</v>
       </c>
       <c r="R130" t="n">
-        <v>7316010</v>
+        <v>7316017</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -14346,10 +14346,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118644448</v>
+        <v>118644455</v>
       </c>
       <c r="B131" t="n">
-        <v>91783</v>
+        <v>78129</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14358,25 +14358,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14386,10 +14386,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685200</v>
+        <v>685162</v>
       </c>
       <c r="R131" t="n">
-        <v>7315632</v>
+        <v>7315661</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14452,10 +14452,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118644455</v>
+        <v>118644457</v>
       </c>
       <c r="B132" t="n">
-        <v>78129</v>
+        <v>77416</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14468,21 +14468,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14492,10 +14492,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685162</v>
+        <v>685225</v>
       </c>
       <c r="R132" t="n">
-        <v>7315661</v>
+        <v>7315875</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14558,10 +14558,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118644445</v>
+        <v>118644443</v>
       </c>
       <c r="B133" t="n">
-        <v>56502</v>
+        <v>79102</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14570,46 +14570,38 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685198</v>
+        <v>685022</v>
       </c>
       <c r="R133" t="n">
-        <v>7315723</v>
+        <v>7316011</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -14642,11 +14634,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14677,10 +14664,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118644449</v>
+        <v>118644451</v>
       </c>
       <c r="B134" t="n">
-        <v>91795</v>
+        <v>78566</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14693,21 +14680,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2059</v>
+        <v>864</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14717,10 +14704,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685163</v>
+        <v>685148</v>
       </c>
       <c r="R134" t="n">
-        <v>7315675</v>
+        <v>7315650</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -14783,10 +14770,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118644458</v>
+        <v>118644449</v>
       </c>
       <c r="B135" t="n">
-        <v>77868</v>
+        <v>91795</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14799,21 +14786,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6437</v>
+        <v>2059</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14823,10 +14810,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685225</v>
+        <v>685163</v>
       </c>
       <c r="R135" t="n">
-        <v>7315875</v>
+        <v>7315675</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14889,10 +14876,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118644451</v>
+        <v>118644440</v>
       </c>
       <c r="B136" t="n">
-        <v>78566</v>
+        <v>74596</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14905,21 +14892,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14929,10 +14916,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685148</v>
+        <v>685139</v>
       </c>
       <c r="R136" t="n">
-        <v>7315650</v>
+        <v>7315644</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15101,10 +15088,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118644444</v>
+        <v>118644454</v>
       </c>
       <c r="B138" t="n">
-        <v>79073</v>
+        <v>90749</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15113,25 +15100,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15141,10 +15128,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685043</v>
+        <v>685052</v>
       </c>
       <c r="R138" t="n">
-        <v>7316017</v>
+        <v>7316025</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -15207,10 +15194,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118644443</v>
+        <v>118644445</v>
       </c>
       <c r="B139" t="n">
-        <v>79102</v>
+        <v>56502</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15219,38 +15206,46 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685022</v>
+        <v>685198</v>
       </c>
       <c r="R139" t="n">
-        <v>7316011</v>
+        <v>7315723</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15283,6 +15278,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15313,10 +15313,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118644440</v>
+        <v>118644458</v>
       </c>
       <c r="B140" t="n">
-        <v>74596</v>
+        <v>77868</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15329,21 +15329,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15353,10 +15353,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685139</v>
+        <v>685225</v>
       </c>
       <c r="R140" t="n">
-        <v>7315644</v>
+        <v>7315875</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -9253,10 +9253,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118642382</v>
+        <v>118640601</v>
       </c>
       <c r="B83" t="n">
-        <v>91779</v>
+        <v>78227</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9265,25 +9265,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9293,13 +9293,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>685188</v>
+        <v>685239</v>
       </c>
       <c r="R83" t="n">
-        <v>7315970</v>
+        <v>7315772</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9343,12 +9343,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9359,10 +9359,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118642383</v>
+        <v>118642377</v>
       </c>
       <c r="B84" t="n">
-        <v>91779</v>
+        <v>78228</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9371,25 +9371,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9399,10 +9399,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>685019</v>
+        <v>685147</v>
       </c>
       <c r="R84" t="n">
-        <v>7316024</v>
+        <v>7315691</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9465,10 +9465,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118640432</v>
+        <v>118640606</v>
       </c>
       <c r="B85" t="n">
-        <v>91795</v>
+        <v>91786</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9477,38 +9477,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>685169</v>
+        <v>685216</v>
       </c>
       <c r="R85" t="n">
-        <v>7315682</v>
+        <v>7315926</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -9555,12 +9555,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9571,10 +9571,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118640610</v>
+        <v>118640590</v>
       </c>
       <c r="B86" t="n">
-        <v>77416</v>
+        <v>79109</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9587,21 +9587,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9611,10 +9611,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>685226</v>
+        <v>685237</v>
       </c>
       <c r="R86" t="n">
-        <v>7315821</v>
+        <v>7315783</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
@@ -9677,10 +9677,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118640595</v>
+        <v>118642384</v>
       </c>
       <c r="B87" t="n">
-        <v>79073</v>
+        <v>77423</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9693,21 +9693,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9717,13 +9717,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>685042</v>
+        <v>685281</v>
       </c>
       <c r="R87" t="n">
-        <v>7316018</v>
+        <v>7315800</v>
       </c>
       <c r="S87" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9767,12 +9767,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9783,10 +9783,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118640592</v>
+        <v>118640610</v>
       </c>
       <c r="B88" t="n">
-        <v>79102</v>
+        <v>77423</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9799,21 +9799,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>685017</v>
+        <v>685226</v>
       </c>
       <c r="R88" t="n">
-        <v>7316004</v>
+        <v>7315821</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
@@ -9889,10 +9889,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118640591</v>
+        <v>118640602</v>
       </c>
       <c r="B89" t="n">
-        <v>79102</v>
+        <v>78573</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9905,21 +9905,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>685079</v>
+        <v>685142</v>
       </c>
       <c r="R89" t="n">
-        <v>7316003</v>
+        <v>7315652</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
@@ -9995,10 +9995,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118640594</v>
+        <v>118640592</v>
       </c>
       <c r="B90" t="n">
-        <v>79073</v>
+        <v>79109</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10011,21 +10011,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10035,10 +10035,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>685213</v>
+        <v>685017</v>
       </c>
       <c r="R90" t="n">
-        <v>7315728</v>
+        <v>7316004</v>
       </c>
       <c r="S90" t="n">
         <v>1</v>
@@ -10101,10 +10101,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118640588</v>
+        <v>118640612</v>
       </c>
       <c r="B91" t="n">
-        <v>74596</v>
+        <v>77875</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10117,21 +10117,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10141,10 +10141,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>685142</v>
+        <v>685222</v>
       </c>
       <c r="R91" t="n">
-        <v>7315652</v>
+        <v>7315868</v>
       </c>
       <c r="S91" t="n">
         <v>1</v>
@@ -10207,10 +10207,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118640438</v>
+        <v>118642382</v>
       </c>
       <c r="B92" t="n">
-        <v>91779</v>
+        <v>91786</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10243,17 +10243,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>685156</v>
+        <v>685188</v>
       </c>
       <c r="R92" t="n">
-        <v>7315676</v>
+        <v>7315970</v>
       </c>
       <c r="S92" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10297,12 +10297,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10313,10 +10313,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118640437</v>
+        <v>118640591</v>
       </c>
       <c r="B93" t="n">
-        <v>78484</v>
+        <v>79109</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10329,34 +10329,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>685190</v>
+        <v>685079</v>
       </c>
       <c r="R93" t="n">
-        <v>7315965</v>
+        <v>7316003</v>
       </c>
       <c r="S93" t="n">
         <v>1</v>
@@ -10403,12 +10403,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10419,10 +10419,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118642374</v>
+        <v>118640588</v>
       </c>
       <c r="B94" t="n">
-        <v>79073</v>
+        <v>74603</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10435,21 +10435,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10459,13 +10459,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>685042</v>
+        <v>685142</v>
       </c>
       <c r="R94" t="n">
-        <v>7316013</v>
+        <v>7315652</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10509,12 +10509,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10525,10 +10525,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118640604</v>
+        <v>118640594</v>
       </c>
       <c r="B95" t="n">
-        <v>90749</v>
+        <v>79080</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10537,25 +10537,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10565,10 +10565,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>685053</v>
+        <v>685213</v>
       </c>
       <c r="R95" t="n">
-        <v>7316028</v>
+        <v>7315728</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
@@ -10631,10 +10631,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118640440</v>
+        <v>118640595</v>
       </c>
       <c r="B96" t="n">
-        <v>91779</v>
+        <v>79080</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10643,38 +10643,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>685191</v>
+        <v>685042</v>
       </c>
       <c r="R96" t="n">
-        <v>7315970</v>
+        <v>7316018</v>
       </c>
       <c r="S96" t="n">
         <v>1</v>
@@ -10721,12 +10721,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10737,10 +10737,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118640430</v>
+        <v>118640600</v>
       </c>
       <c r="B97" t="n">
-        <v>79102</v>
+        <v>78228</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10753,34 +10753,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>685242</v>
+        <v>685180</v>
       </c>
       <c r="R97" t="n">
-        <v>7315784</v>
+        <v>7315662</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -10827,12 +10827,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10843,10 +10843,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118640601</v>
+        <v>118642383</v>
       </c>
       <c r="B98" t="n">
-        <v>78220</v>
+        <v>91786</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10855,25 +10855,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10883,13 +10883,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>685239</v>
+        <v>685019</v>
       </c>
       <c r="R98" t="n">
-        <v>7315772</v>
+        <v>7316024</v>
       </c>
       <c r="S98" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10933,12 +10933,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10949,10 +10949,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118642386</v>
+        <v>118640440</v>
       </c>
       <c r="B99" t="n">
-        <v>77416</v>
+        <v>91786</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10961,41 +10961,41 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>685239</v>
+        <v>685191</v>
       </c>
       <c r="R99" t="n">
-        <v>7315866</v>
+        <v>7315970</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11039,12 +11039,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11055,10 +11055,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118640606</v>
+        <v>118642378</v>
       </c>
       <c r="B100" t="n">
-        <v>91779</v>
+        <v>90756</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11067,25 +11067,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11095,13 +11095,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>685216</v>
+        <v>685056</v>
       </c>
       <c r="R100" t="n">
-        <v>7315926</v>
+        <v>7316028</v>
       </c>
       <c r="S100" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11145,12 +11145,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11161,10 +11161,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118642378</v>
+        <v>118640432</v>
       </c>
       <c r="B101" t="n">
-        <v>90749</v>
+        <v>91802</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11173,41 +11173,41 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>65</v>
+        <v>2059</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>685056</v>
+        <v>685169</v>
       </c>
       <c r="R101" t="n">
-        <v>7316028</v>
+        <v>7315682</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11251,12 +11251,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11267,10 +11267,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118642384</v>
+        <v>118640609</v>
       </c>
       <c r="B102" t="n">
-        <v>77416</v>
+        <v>91786</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11279,25 +11279,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11307,13 +11307,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>685281</v>
+        <v>685029</v>
       </c>
       <c r="R102" t="n">
-        <v>7315800</v>
+        <v>7316018</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11357,12 +11357,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11373,10 +11373,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118640590</v>
+        <v>118642386</v>
       </c>
       <c r="B103" t="n">
-        <v>79102</v>
+        <v>77423</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11389,21 +11389,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11413,13 +11413,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>685237</v>
+        <v>685239</v>
       </c>
       <c r="R103" t="n">
-        <v>7315783</v>
+        <v>7315866</v>
       </c>
       <c r="S103" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11463,12 +11463,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11479,10 +11479,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118640611</v>
+        <v>118640608</v>
       </c>
       <c r="B104" t="n">
-        <v>77416</v>
+        <v>91786</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11491,25 +11491,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11519,10 +11519,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>685210</v>
+        <v>685209</v>
       </c>
       <c r="R104" t="n">
-        <v>7315857</v>
+        <v>7315725</v>
       </c>
       <c r="S104" t="n">
         <v>1</v>
@@ -11585,10 +11585,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118640612</v>
+        <v>118640437</v>
       </c>
       <c r="B105" t="n">
-        <v>77868</v>
+        <v>78491</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11601,34 +11601,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>685222</v>
+        <v>685190</v>
       </c>
       <c r="R105" t="n">
-        <v>7315868</v>
+        <v>7315965</v>
       </c>
       <c r="S105" t="n">
         <v>1</v>
@@ -11675,12 +11675,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11691,10 +11691,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118640609</v>
+        <v>118642374</v>
       </c>
       <c r="B106" t="n">
-        <v>91779</v>
+        <v>79080</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11703,25 +11703,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11731,13 +11731,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>685029</v>
+        <v>685042</v>
       </c>
       <c r="R106" t="n">
-        <v>7316018</v>
+        <v>7316013</v>
       </c>
       <c r="S106" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11781,12 +11781,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11797,10 +11797,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118640602</v>
+        <v>118640607</v>
       </c>
       <c r="B107" t="n">
-        <v>78566</v>
+        <v>91786</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11809,25 +11809,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11837,10 +11837,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>685142</v>
+        <v>685156</v>
       </c>
       <c r="R107" t="n">
-        <v>7315652</v>
+        <v>7315668</v>
       </c>
       <c r="S107" t="n">
         <v>1</v>
@@ -11903,10 +11903,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118640608</v>
+        <v>118640430</v>
       </c>
       <c r="B108" t="n">
-        <v>91779</v>
+        <v>79109</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11915,38 +11915,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>685209</v>
+        <v>685242</v>
       </c>
       <c r="R108" t="n">
-        <v>7315725</v>
+        <v>7315784</v>
       </c>
       <c r="S108" t="n">
         <v>1</v>
@@ -11993,12 +11993,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -12009,10 +12009,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118640607</v>
+        <v>118640438</v>
       </c>
       <c r="B109" t="n">
-        <v>91779</v>
+        <v>91786</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12045,14 +12045,14 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
         <v>685156</v>
       </c>
       <c r="R109" t="n">
-        <v>7315668</v>
+        <v>7315676</v>
       </c>
       <c r="S109" t="n">
         <v>1</v>
@@ -12099,12 +12099,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -12115,10 +12115,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118640600</v>
+        <v>118640604</v>
       </c>
       <c r="B110" t="n">
-        <v>78221</v>
+        <v>90756</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12127,25 +12127,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12155,10 +12155,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>685180</v>
+        <v>685053</v>
       </c>
       <c r="R110" t="n">
-        <v>7315662</v>
+        <v>7316028</v>
       </c>
       <c r="S110" t="n">
         <v>1</v>
@@ -12221,10 +12221,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118642377</v>
+        <v>118640611</v>
       </c>
       <c r="B111" t="n">
-        <v>78221</v>
+        <v>77423</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12237,21 +12237,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>685147</v>
+        <v>685210</v>
       </c>
       <c r="R111" t="n">
-        <v>7315691</v>
+        <v>7315857</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12311,12 +12311,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12327,10 +12327,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118640790</v>
+        <v>118640775</v>
       </c>
       <c r="B112" t="n">
-        <v>91779</v>
+        <v>79080</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12339,25 +12339,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>685230</v>
+        <v>685170</v>
       </c>
       <c r="R112" t="n">
-        <v>7315855</v>
+        <v>7315649</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12433,10 +12433,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118640791</v>
+        <v>118640790</v>
       </c>
       <c r="B113" t="n">
-        <v>91779</v>
+        <v>91786</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12473,10 +12473,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>685240</v>
+        <v>685230</v>
       </c>
       <c r="R113" t="n">
-        <v>7315893</v>
+        <v>7315855</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12539,10 +12539,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118640781</v>
+        <v>118640773</v>
       </c>
       <c r="B114" t="n">
-        <v>91795</v>
+        <v>79109</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12555,21 +12555,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12579,10 +12579,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>685168</v>
+        <v>685201</v>
       </c>
       <c r="R114" t="n">
-        <v>7315680</v>
+        <v>7315735</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12645,10 +12645,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118640774</v>
+        <v>118661409</v>
       </c>
       <c r="B115" t="n">
-        <v>79102</v>
+        <v>91786</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12657,38 +12657,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Suddesjsure, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>685022</v>
+        <v>685192</v>
       </c>
       <c r="R115" t="n">
-        <v>7316004</v>
+        <v>7315652</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12735,12 +12735,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12751,10 +12751,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118640788</v>
+        <v>118640785</v>
       </c>
       <c r="B116" t="n">
-        <v>90749</v>
+        <v>78227</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12763,25 +12763,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12791,10 +12791,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>685048</v>
+        <v>685195</v>
       </c>
       <c r="R116" t="n">
-        <v>7316017</v>
+        <v>7315739</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12835,6 +12835,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12857,10 +12858,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118640773</v>
+        <v>118640784</v>
       </c>
       <c r="B117" t="n">
-        <v>79102</v>
+        <v>80448</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12873,21 +12874,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12897,10 +12898,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>685201</v>
+        <v>685196</v>
       </c>
       <c r="R117" t="n">
-        <v>7315735</v>
+        <v>7315737</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12963,10 +12964,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118640785</v>
+        <v>118640791</v>
       </c>
       <c r="B118" t="n">
-        <v>78220</v>
+        <v>91786</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12975,25 +12976,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13003,10 +13004,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685195</v>
+        <v>685240</v>
       </c>
       <c r="R118" t="n">
-        <v>7315739</v>
+        <v>7315893</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13047,7 +13048,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13073,7 +13073,7 @@
         <v>118640776</v>
       </c>
       <c r="B119" t="n">
-        <v>79073</v>
+        <v>79080</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13176,10 +13176,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118640784</v>
+        <v>118640781</v>
       </c>
       <c r="B120" t="n">
-        <v>80441</v>
+        <v>91802</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13192,21 +13192,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1049</v>
+        <v>2059</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13216,10 +13216,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685196</v>
+        <v>685168</v>
       </c>
       <c r="R120" t="n">
-        <v>7315737</v>
+        <v>7315680</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13282,10 +13282,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118661409</v>
+        <v>118640778</v>
       </c>
       <c r="B121" t="n">
-        <v>91779</v>
+        <v>91790</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13294,38 +13294,38 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjsure, Pi lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685192</v>
+        <v>685199</v>
       </c>
       <c r="R121" t="n">
-        <v>7315652</v>
+        <v>7315633</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13372,12 +13372,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13388,10 +13388,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118640775</v>
+        <v>118640792</v>
       </c>
       <c r="B122" t="n">
-        <v>79073</v>
+        <v>91786</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13400,25 +13400,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13428,10 +13428,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>685170</v>
+        <v>685179</v>
       </c>
       <c r="R122" t="n">
-        <v>7315649</v>
+        <v>7315961</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13497,7 +13497,7 @@
         <v>118661410</v>
       </c>
       <c r="B123" t="n">
-        <v>91779</v>
+        <v>91786</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13600,10 +13600,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118640792</v>
+        <v>118640774</v>
       </c>
       <c r="B124" t="n">
-        <v>91779</v>
+        <v>79109</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13612,25 +13612,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13640,10 +13640,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685179</v>
+        <v>685022</v>
       </c>
       <c r="R124" t="n">
-        <v>7315961</v>
+        <v>7316004</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13706,10 +13706,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118640778</v>
+        <v>118640788</v>
       </c>
       <c r="B125" t="n">
-        <v>91783</v>
+        <v>90756</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13722,21 +13722,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4365</v>
+        <v>65</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13746,10 +13746,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685199</v>
+        <v>685048</v>
       </c>
       <c r="R125" t="n">
-        <v>7315633</v>
+        <v>7316017</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13812,10 +13812,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118644456</v>
+        <v>118644445</v>
       </c>
       <c r="B126" t="n">
-        <v>91779</v>
+        <v>56502</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13828,34 +13828,42 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685013</v>
+        <v>685198</v>
       </c>
       <c r="R126" t="n">
-        <v>7316010</v>
+        <v>7315723</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -13888,6 +13896,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13918,10 +13931,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118644450</v>
+        <v>118644443</v>
       </c>
       <c r="B127" t="n">
-        <v>78220</v>
+        <v>79109</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13934,21 +13947,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13958,10 +13971,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>685140</v>
+        <v>685022</v>
       </c>
       <c r="R127" t="n">
-        <v>7315969</v>
+        <v>7316011</v>
       </c>
       <c r="S127" t="n">
         <v>15</v>
@@ -14024,10 +14037,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118644448</v>
+        <v>118644454</v>
       </c>
       <c r="B128" t="n">
-        <v>91783</v>
+        <v>90756</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14040,21 +14053,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4365</v>
+        <v>65</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14064,10 +14077,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685200</v>
+        <v>685052</v>
       </c>
       <c r="R128" t="n">
-        <v>7315632</v>
+        <v>7316025</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -14130,10 +14143,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118640783</v>
+        <v>118644444</v>
       </c>
       <c r="B129" t="n">
-        <v>78221</v>
+        <v>79080</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14146,40 +14159,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Suddesjsure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685195</v>
+        <v>685043</v>
       </c>
       <c r="R129" t="n">
-        <v>7315735</v>
+        <v>7316017</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14217,19 +14227,18 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14240,10 +14249,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118644444</v>
+        <v>118640783</v>
       </c>
       <c r="B130" t="n">
-        <v>79073</v>
+        <v>78228</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14256,37 +14265,40 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjsure, Pi lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685043</v>
+        <v>685195</v>
       </c>
       <c r="R130" t="n">
-        <v>7316017</v>
+        <v>7315735</v>
       </c>
       <c r="S130" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14324,18 +14336,19 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14346,10 +14359,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118644455</v>
+        <v>118644450</v>
       </c>
       <c r="B131" t="n">
-        <v>78129</v>
+        <v>78227</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14362,21 +14375,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14386,10 +14399,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685162</v>
+        <v>685140</v>
       </c>
       <c r="R131" t="n">
-        <v>7315661</v>
+        <v>7315969</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14452,10 +14465,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118644457</v>
+        <v>118644458</v>
       </c>
       <c r="B132" t="n">
-        <v>77416</v>
+        <v>77875</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14468,21 +14481,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14558,10 +14571,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118644443</v>
+        <v>118644451</v>
       </c>
       <c r="B133" t="n">
-        <v>79102</v>
+        <v>78573</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14574,21 +14587,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14598,10 +14611,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685022</v>
+        <v>685148</v>
       </c>
       <c r="R133" t="n">
-        <v>7316011</v>
+        <v>7315650</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -14664,10 +14677,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118644451</v>
+        <v>118644449</v>
       </c>
       <c r="B134" t="n">
-        <v>78566</v>
+        <v>91802</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14680,21 +14693,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>864</v>
+        <v>2059</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14704,10 +14717,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685148</v>
+        <v>685163</v>
       </c>
       <c r="R134" t="n">
-        <v>7315650</v>
+        <v>7315675</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -14770,10 +14783,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118644449</v>
+        <v>118644453</v>
       </c>
       <c r="B135" t="n">
-        <v>91795</v>
+        <v>78491</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14786,21 +14799,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14810,10 +14823,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685163</v>
+        <v>685164</v>
       </c>
       <c r="R135" t="n">
-        <v>7315675</v>
+        <v>7315966</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14876,10 +14889,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118644440</v>
+        <v>118644456</v>
       </c>
       <c r="B136" t="n">
-        <v>74596</v>
+        <v>91786</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14888,25 +14901,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14916,10 +14929,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685139</v>
+        <v>685013</v>
       </c>
       <c r="R136" t="n">
-        <v>7315644</v>
+        <v>7316010</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14982,10 +14995,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118644453</v>
+        <v>118644455</v>
       </c>
       <c r="B137" t="n">
-        <v>78484</v>
+        <v>78136</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14998,21 +15011,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15022,10 +15035,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685164</v>
+        <v>685162</v>
       </c>
       <c r="R137" t="n">
-        <v>7315966</v>
+        <v>7315661</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15088,10 +15101,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118644454</v>
+        <v>118644457</v>
       </c>
       <c r="B138" t="n">
-        <v>90749</v>
+        <v>77423</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15100,25 +15113,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>65</v>
+        <v>6487</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15128,10 +15141,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685052</v>
+        <v>685225</v>
       </c>
       <c r="R138" t="n">
-        <v>7316025</v>
+        <v>7315875</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -15194,10 +15207,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118644445</v>
+        <v>118644440</v>
       </c>
       <c r="B139" t="n">
-        <v>56502</v>
+        <v>74603</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15206,46 +15219,38 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685198</v>
+        <v>685139</v>
       </c>
       <c r="R139" t="n">
-        <v>7315723</v>
+        <v>7315644</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15278,11 +15283,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15313,10 +15313,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118644458</v>
+        <v>118644448</v>
       </c>
       <c r="B140" t="n">
-        <v>77868</v>
+        <v>91790</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15325,25 +15325,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6437</v>
+        <v>4365</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15353,10 +15353,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685225</v>
+        <v>685200</v>
       </c>
       <c r="R140" t="n">
-        <v>7315875</v>
+        <v>7315632</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -9465,10 +9465,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118640606</v>
+        <v>118640590</v>
       </c>
       <c r="B85" t="n">
-        <v>91786</v>
+        <v>79109</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9477,25 +9477,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9505,10 +9505,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>685216</v>
+        <v>685237</v>
       </c>
       <c r="R85" t="n">
-        <v>7315926</v>
+        <v>7315783</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -9571,10 +9571,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118640590</v>
+        <v>118640606</v>
       </c>
       <c r="B86" t="n">
-        <v>79109</v>
+        <v>91786</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9583,25 +9583,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9611,10 +9611,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>685237</v>
+        <v>685216</v>
       </c>
       <c r="R86" t="n">
-        <v>7315783</v>
+        <v>7315926</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -9253,10 +9253,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118640601</v>
+        <v>118642378</v>
       </c>
       <c r="B83" t="n">
-        <v>78227</v>
+        <v>90756</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9265,25 +9265,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>65</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9293,13 +9293,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>685239</v>
+        <v>685056</v>
       </c>
       <c r="R83" t="n">
-        <v>7315772</v>
+        <v>7316028</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9343,12 +9343,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9359,10 +9359,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118642377</v>
+        <v>118640594</v>
       </c>
       <c r="B84" t="n">
-        <v>78228</v>
+        <v>79080</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9375,21 +9375,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9399,13 +9399,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>685147</v>
+        <v>685213</v>
       </c>
       <c r="R84" t="n">
-        <v>7315691</v>
+        <v>7315728</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9449,12 +9449,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9465,10 +9465,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118640590</v>
+        <v>118642386</v>
       </c>
       <c r="B85" t="n">
-        <v>79109</v>
+        <v>77423</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9481,21 +9481,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9505,13 +9505,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>685237</v>
+        <v>685239</v>
       </c>
       <c r="R85" t="n">
-        <v>7315783</v>
+        <v>7315866</v>
       </c>
       <c r="S85" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9555,12 +9555,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9571,7 +9571,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118640606</v>
+        <v>118640440</v>
       </c>
       <c r="B86" t="n">
         <v>91786</v>
@@ -9607,14 +9607,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>685216</v>
+        <v>685191</v>
       </c>
       <c r="R86" t="n">
-        <v>7315926</v>
+        <v>7315970</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
@@ -9661,12 +9661,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9677,10 +9677,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118642384</v>
+        <v>118642382</v>
       </c>
       <c r="B87" t="n">
-        <v>77423</v>
+        <v>91786</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9689,25 +9689,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9717,10 +9717,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>685281</v>
+        <v>685188</v>
       </c>
       <c r="R87" t="n">
-        <v>7315800</v>
+        <v>7315970</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9783,10 +9783,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118640610</v>
+        <v>118640437</v>
       </c>
       <c r="B88" t="n">
-        <v>77423</v>
+        <v>78491</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9799,34 +9799,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>685226</v>
+        <v>685190</v>
       </c>
       <c r="R88" t="n">
-        <v>7315821</v>
+        <v>7315965</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
@@ -9873,12 +9873,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9889,10 +9889,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118640602</v>
+        <v>118640601</v>
       </c>
       <c r="B89" t="n">
-        <v>78573</v>
+        <v>78227</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9905,21 +9905,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>864</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>685142</v>
+        <v>685239</v>
       </c>
       <c r="R89" t="n">
-        <v>7315652</v>
+        <v>7315772</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
@@ -9995,10 +9995,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118640592</v>
+        <v>118640609</v>
       </c>
       <c r="B90" t="n">
-        <v>79109</v>
+        <v>91786</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10007,25 +10007,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10035,10 +10035,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>685017</v>
+        <v>685029</v>
       </c>
       <c r="R90" t="n">
-        <v>7316004</v>
+        <v>7316018</v>
       </c>
       <c r="S90" t="n">
         <v>1</v>
@@ -10101,10 +10101,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118640612</v>
+        <v>118640607</v>
       </c>
       <c r="B91" t="n">
-        <v>77875</v>
+        <v>91786</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10113,25 +10113,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10141,10 +10141,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>685222</v>
+        <v>685156</v>
       </c>
       <c r="R91" t="n">
-        <v>7315868</v>
+        <v>7315668</v>
       </c>
       <c r="S91" t="n">
         <v>1</v>
@@ -10207,10 +10207,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118642382</v>
+        <v>118640591</v>
       </c>
       <c r="B92" t="n">
-        <v>91786</v>
+        <v>79109</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10219,25 +10219,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10247,13 +10247,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>685188</v>
+        <v>685079</v>
       </c>
       <c r="R92" t="n">
-        <v>7315970</v>
+        <v>7316003</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10297,12 +10297,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10313,10 +10313,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118640591</v>
+        <v>118640438</v>
       </c>
       <c r="B93" t="n">
-        <v>79109</v>
+        <v>91786</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10325,38 +10325,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>685079</v>
+        <v>685156</v>
       </c>
       <c r="R93" t="n">
-        <v>7316003</v>
+        <v>7315676</v>
       </c>
       <c r="S93" t="n">
         <v>1</v>
@@ -10403,12 +10403,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10419,10 +10419,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118640588</v>
+        <v>118640611</v>
       </c>
       <c r="B94" t="n">
-        <v>74603</v>
+        <v>77423</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10435,21 +10435,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>6487</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10459,10 +10459,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>685142</v>
+        <v>685210</v>
       </c>
       <c r="R94" t="n">
-        <v>7315652</v>
+        <v>7315857</v>
       </c>
       <c r="S94" t="n">
         <v>1</v>
@@ -10525,10 +10525,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118640594</v>
+        <v>118640600</v>
       </c>
       <c r="B95" t="n">
-        <v>79080</v>
+        <v>78228</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10541,21 +10541,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10565,10 +10565,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>685213</v>
+        <v>685180</v>
       </c>
       <c r="R95" t="n">
-        <v>7315728</v>
+        <v>7315662</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
@@ -10737,10 +10737,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118640600</v>
+        <v>118640606</v>
       </c>
       <c r="B97" t="n">
-        <v>78228</v>
+        <v>91786</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10749,25 +10749,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10777,10 +10777,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>685180</v>
+        <v>685216</v>
       </c>
       <c r="R97" t="n">
-        <v>7315662</v>
+        <v>7315926</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -10843,10 +10843,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118642383</v>
+        <v>118640590</v>
       </c>
       <c r="B98" t="n">
-        <v>91786</v>
+        <v>79109</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10855,25 +10855,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10883,13 +10883,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>685019</v>
+        <v>685237</v>
       </c>
       <c r="R98" t="n">
-        <v>7316024</v>
+        <v>7315783</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10933,12 +10933,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10949,10 +10949,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118640440</v>
+        <v>118642384</v>
       </c>
       <c r="B99" t="n">
-        <v>91786</v>
+        <v>77423</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10961,41 +10961,41 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>685191</v>
+        <v>685281</v>
       </c>
       <c r="R99" t="n">
-        <v>7315970</v>
+        <v>7315800</v>
       </c>
       <c r="S99" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11039,12 +11039,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11055,10 +11055,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118642378</v>
+        <v>118640592</v>
       </c>
       <c r="B100" t="n">
-        <v>90756</v>
+        <v>79109</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11067,25 +11067,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11095,13 +11095,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>685056</v>
+        <v>685017</v>
       </c>
       <c r="R100" t="n">
-        <v>7316028</v>
+        <v>7316004</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11145,12 +11145,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11161,10 +11161,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118640432</v>
+        <v>118640430</v>
       </c>
       <c r="B101" t="n">
-        <v>91802</v>
+        <v>79109</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11177,21 +11177,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11201,10 +11201,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>685169</v>
+        <v>685242</v>
       </c>
       <c r="R101" t="n">
-        <v>7315682</v>
+        <v>7315784</v>
       </c>
       <c r="S101" t="n">
         <v>1</v>
@@ -11267,10 +11267,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118640609</v>
+        <v>118640612</v>
       </c>
       <c r="B102" t="n">
-        <v>91786</v>
+        <v>77875</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11279,25 +11279,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11307,10 +11307,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>685029</v>
+        <v>685222</v>
       </c>
       <c r="R102" t="n">
-        <v>7316018</v>
+        <v>7315868</v>
       </c>
       <c r="S102" t="n">
         <v>1</v>
@@ -11373,10 +11373,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118642386</v>
+        <v>118642377</v>
       </c>
       <c r="B103" t="n">
-        <v>77423</v>
+        <v>78228</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11389,21 +11389,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11413,10 +11413,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>685239</v>
+        <v>685147</v>
       </c>
       <c r="R103" t="n">
-        <v>7315866</v>
+        <v>7315691</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11479,10 +11479,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118640608</v>
+        <v>118642374</v>
       </c>
       <c r="B104" t="n">
-        <v>91786</v>
+        <v>79080</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11491,25 +11491,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11519,13 +11519,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>685209</v>
+        <v>685042</v>
       </c>
       <c r="R104" t="n">
-        <v>7315725</v>
+        <v>7316013</v>
       </c>
       <c r="S104" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11569,12 +11569,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11585,10 +11585,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118640437</v>
+        <v>118640604</v>
       </c>
       <c r="B105" t="n">
-        <v>78491</v>
+        <v>90756</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11597,38 +11597,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>685190</v>
+        <v>685053</v>
       </c>
       <c r="R105" t="n">
-        <v>7315965</v>
+        <v>7316028</v>
       </c>
       <c r="S105" t="n">
         <v>1</v>
@@ -11675,12 +11675,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11691,10 +11691,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118642374</v>
+        <v>118640588</v>
       </c>
       <c r="B106" t="n">
-        <v>79080</v>
+        <v>74603</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11707,21 +11707,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11731,13 +11731,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>685042</v>
+        <v>685142</v>
       </c>
       <c r="R106" t="n">
-        <v>7316013</v>
+        <v>7315652</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11781,12 +11781,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11797,7 +11797,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118640607</v>
+        <v>118640608</v>
       </c>
       <c r="B107" t="n">
         <v>91786</v>
@@ -11837,10 +11837,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>685156</v>
+        <v>685209</v>
       </c>
       <c r="R107" t="n">
-        <v>7315668</v>
+        <v>7315725</v>
       </c>
       <c r="S107" t="n">
         <v>1</v>
@@ -11903,10 +11903,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118640430</v>
+        <v>118640432</v>
       </c>
       <c r="B108" t="n">
-        <v>79109</v>
+        <v>91802</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11919,21 +11919,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11943,10 +11943,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>685242</v>
+        <v>685169</v>
       </c>
       <c r="R108" t="n">
-        <v>7315784</v>
+        <v>7315682</v>
       </c>
       <c r="S108" t="n">
         <v>1</v>
@@ -12009,10 +12009,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118640438</v>
+        <v>118640610</v>
       </c>
       <c r="B109" t="n">
-        <v>91786</v>
+        <v>77423</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12021,38 +12021,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>685156</v>
+        <v>685226</v>
       </c>
       <c r="R109" t="n">
-        <v>7315676</v>
+        <v>7315821</v>
       </c>
       <c r="S109" t="n">
         <v>1</v>
@@ -12099,12 +12099,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -12115,10 +12115,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118640604</v>
+        <v>118642383</v>
       </c>
       <c r="B110" t="n">
-        <v>90756</v>
+        <v>91786</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12127,25 +12127,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12155,13 +12155,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>685053</v>
+        <v>685019</v>
       </c>
       <c r="R110" t="n">
-        <v>7316028</v>
+        <v>7316024</v>
       </c>
       <c r="S110" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12205,12 +12205,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -12221,10 +12221,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118640611</v>
+        <v>118640602</v>
       </c>
       <c r="B111" t="n">
-        <v>77423</v>
+        <v>78573</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12237,21 +12237,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6487</v>
+        <v>864</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12261,10 +12261,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>685210</v>
+        <v>685142</v>
       </c>
       <c r="R111" t="n">
-        <v>7315857</v>
+        <v>7315652</v>
       </c>
       <c r="S111" t="n">
         <v>1</v>
@@ -12327,10 +12327,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118640775</v>
+        <v>118640785</v>
       </c>
       <c r="B112" t="n">
-        <v>79080</v>
+        <v>78227</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12343,21 +12343,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>685170</v>
+        <v>685195</v>
       </c>
       <c r="R112" t="n">
-        <v>7315649</v>
+        <v>7315739</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12411,6 +12411,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12433,10 +12434,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118640790</v>
+        <v>118640788</v>
       </c>
       <c r="B113" t="n">
-        <v>91786</v>
+        <v>90756</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12445,25 +12446,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12473,10 +12474,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>685230</v>
+        <v>685048</v>
       </c>
       <c r="R113" t="n">
-        <v>7315855</v>
+        <v>7316017</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12539,10 +12540,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118640773</v>
+        <v>118661410</v>
       </c>
       <c r="B114" t="n">
-        <v>79109</v>
+        <v>91786</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12551,38 +12552,38 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Suddesjsure, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>685201</v>
+        <v>685231</v>
       </c>
       <c r="R114" t="n">
-        <v>7315735</v>
+        <v>7315731</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12629,12 +12630,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12645,10 +12646,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118661409</v>
+        <v>118640784</v>
       </c>
       <c r="B115" t="n">
-        <v>91786</v>
+        <v>80448</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12657,38 +12658,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjsure, Pi lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>685192</v>
+        <v>685196</v>
       </c>
       <c r="R115" t="n">
-        <v>7315652</v>
+        <v>7315737</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12735,12 +12736,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12751,10 +12752,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118640785</v>
+        <v>118640790</v>
       </c>
       <c r="B116" t="n">
-        <v>78227</v>
+        <v>91786</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12763,25 +12764,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12791,10 +12792,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>685195</v>
+        <v>685230</v>
       </c>
       <c r="R116" t="n">
-        <v>7315739</v>
+        <v>7315855</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12835,7 +12836,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12858,10 +12858,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118640784</v>
+        <v>118640773</v>
       </c>
       <c r="B117" t="n">
-        <v>80448</v>
+        <v>79109</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12874,21 +12874,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12898,10 +12898,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>685196</v>
+        <v>685201</v>
       </c>
       <c r="R117" t="n">
-        <v>7315737</v>
+        <v>7315735</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12964,7 +12964,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118640791</v>
+        <v>118661409</v>
       </c>
       <c r="B118" t="n">
         <v>91786</v>
@@ -13000,14 +13000,14 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Suddesjsure, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685240</v>
+        <v>685192</v>
       </c>
       <c r="R118" t="n">
-        <v>7315893</v>
+        <v>7315652</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13054,12 +13054,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -13070,10 +13070,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118640776</v>
+        <v>118640774</v>
       </c>
       <c r="B119" t="n">
-        <v>79080</v>
+        <v>79109</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13086,21 +13086,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13110,10 +13110,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>685197</v>
+        <v>685022</v>
       </c>
       <c r="R119" t="n">
-        <v>7315733</v>
+        <v>7316004</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13176,10 +13176,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118640781</v>
+        <v>118640778</v>
       </c>
       <c r="B120" t="n">
-        <v>91802</v>
+        <v>91790</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13188,25 +13188,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2059</v>
+        <v>4365</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13216,10 +13216,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685168</v>
+        <v>685199</v>
       </c>
       <c r="R120" t="n">
-        <v>7315680</v>
+        <v>7315633</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13282,10 +13282,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118640778</v>
+        <v>118640776</v>
       </c>
       <c r="B121" t="n">
-        <v>91790</v>
+        <v>79080</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13294,25 +13294,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4365</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685199</v>
+        <v>685197</v>
       </c>
       <c r="R121" t="n">
-        <v>7315633</v>
+        <v>7315733</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13388,10 +13388,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118640792</v>
+        <v>118640781</v>
       </c>
       <c r="B122" t="n">
-        <v>91786</v>
+        <v>91802</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13400,25 +13400,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13428,10 +13428,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>685179</v>
+        <v>685168</v>
       </c>
       <c r="R122" t="n">
-        <v>7315961</v>
+        <v>7315680</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13494,7 +13494,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118661410</v>
+        <v>118640791</v>
       </c>
       <c r="B123" t="n">
         <v>91786</v>
@@ -13530,14 +13530,14 @@
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjsure, Pi lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685231</v>
+        <v>685240</v>
       </c>
       <c r="R123" t="n">
-        <v>7315731</v>
+        <v>7315893</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13584,12 +13584,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Anton Albertsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13600,10 +13600,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118640774</v>
+        <v>118640792</v>
       </c>
       <c r="B124" t="n">
-        <v>79109</v>
+        <v>91786</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13612,25 +13612,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13640,10 +13640,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685022</v>
+        <v>685179</v>
       </c>
       <c r="R124" t="n">
-        <v>7316004</v>
+        <v>7315961</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13706,10 +13706,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118640788</v>
+        <v>118640775</v>
       </c>
       <c r="B125" t="n">
-        <v>90756</v>
+        <v>79080</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13718,25 +13718,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13746,10 +13746,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685048</v>
+        <v>685170</v>
       </c>
       <c r="R125" t="n">
-        <v>7316017</v>
+        <v>7315649</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13812,10 +13812,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118644445</v>
+        <v>118640783</v>
       </c>
       <c r="B126" t="n">
-        <v>56502</v>
+        <v>78228</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13824,49 +13824,44 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjsure, Pi lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685198</v>
+        <v>685195</v>
       </c>
       <c r="R126" t="n">
-        <v>7315723</v>
+        <v>7315735</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13898,29 +13893,25 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13931,10 +13922,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118644443</v>
+        <v>118644458</v>
       </c>
       <c r="B127" t="n">
-        <v>79109</v>
+        <v>77875</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13947,21 +13938,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13971,10 +13962,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>685022</v>
+        <v>685225</v>
       </c>
       <c r="R127" t="n">
-        <v>7316011</v>
+        <v>7315875</v>
       </c>
       <c r="S127" t="n">
         <v>15</v>
@@ -14037,10 +14028,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118644454</v>
+        <v>118644450</v>
       </c>
       <c r="B128" t="n">
-        <v>90756</v>
+        <v>78227</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14049,25 +14040,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14077,10 +14068,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685052</v>
+        <v>685140</v>
       </c>
       <c r="R128" t="n">
-        <v>7316025</v>
+        <v>7315969</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -14143,10 +14134,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118644444</v>
+        <v>118644455</v>
       </c>
       <c r="B129" t="n">
-        <v>79080</v>
+        <v>78136</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14159,21 +14150,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14183,10 +14174,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685043</v>
+        <v>685162</v>
       </c>
       <c r="R129" t="n">
-        <v>7316017</v>
+        <v>7315661</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -14249,10 +14240,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118640783</v>
+        <v>118644444</v>
       </c>
       <c r="B130" t="n">
-        <v>78228</v>
+        <v>79080</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14265,40 +14256,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Suddesjsure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685195</v>
+        <v>685043</v>
       </c>
       <c r="R130" t="n">
-        <v>7315735</v>
+        <v>7316017</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14336,19 +14324,18 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14359,10 +14346,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118644450</v>
+        <v>118644451</v>
       </c>
       <c r="B131" t="n">
-        <v>78227</v>
+        <v>78573</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14375,21 +14362,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>864</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14399,10 +14386,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685140</v>
+        <v>685148</v>
       </c>
       <c r="R131" t="n">
-        <v>7315969</v>
+        <v>7315650</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14465,10 +14452,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118644458</v>
+        <v>118644443</v>
       </c>
       <c r="B132" t="n">
-        <v>77875</v>
+        <v>79109</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14481,21 +14468,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14505,10 +14492,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685225</v>
+        <v>685022</v>
       </c>
       <c r="R132" t="n">
-        <v>7315875</v>
+        <v>7316011</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14571,10 +14558,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118644451</v>
+        <v>118644440</v>
       </c>
       <c r="B133" t="n">
-        <v>78573</v>
+        <v>74603</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14587,21 +14574,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14611,10 +14598,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685148</v>
+        <v>685139</v>
       </c>
       <c r="R133" t="n">
-        <v>7315650</v>
+        <v>7315644</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -14677,10 +14664,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118644449</v>
+        <v>118644454</v>
       </c>
       <c r="B134" t="n">
-        <v>91802</v>
+        <v>90756</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14689,25 +14676,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2059</v>
+        <v>65</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14717,10 +14704,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685163</v>
+        <v>685052</v>
       </c>
       <c r="R134" t="n">
-        <v>7315675</v>
+        <v>7316025</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -14783,10 +14770,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118644453</v>
+        <v>118644456</v>
       </c>
       <c r="B135" t="n">
-        <v>78491</v>
+        <v>91786</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14795,25 +14782,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14823,10 +14810,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685164</v>
+        <v>685013</v>
       </c>
       <c r="R135" t="n">
-        <v>7315966</v>
+        <v>7316010</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14889,10 +14876,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118644456</v>
+        <v>118644445</v>
       </c>
       <c r="B136" t="n">
-        <v>91786</v>
+        <v>56502</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14905,34 +14892,42 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685013</v>
+        <v>685198</v>
       </c>
       <c r="R136" t="n">
-        <v>7316010</v>
+        <v>7315723</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14965,6 +14960,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14995,10 +14995,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118644455</v>
+        <v>118644448</v>
       </c>
       <c r="B137" t="n">
-        <v>78136</v>
+        <v>91790</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15007,25 +15007,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15035,10 +15035,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685162</v>
+        <v>685200</v>
       </c>
       <c r="R137" t="n">
-        <v>7315661</v>
+        <v>7315632</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15101,10 +15101,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118644457</v>
+        <v>118644453</v>
       </c>
       <c r="B138" t="n">
-        <v>77423</v>
+        <v>78491</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15117,21 +15117,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15141,10 +15141,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685225</v>
+        <v>685164</v>
       </c>
       <c r="R138" t="n">
-        <v>7315875</v>
+        <v>7315966</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -15207,10 +15207,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118644440</v>
+        <v>118644457</v>
       </c>
       <c r="B139" t="n">
-        <v>74603</v>
+        <v>77423</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15223,21 +15223,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6440</v>
+        <v>6487</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15247,10 +15247,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685139</v>
+        <v>685225</v>
       </c>
       <c r="R139" t="n">
-        <v>7315644</v>
+        <v>7315875</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15313,10 +15313,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118644448</v>
+        <v>118644449</v>
       </c>
       <c r="B140" t="n">
-        <v>91790</v>
+        <v>91802</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15325,25 +15325,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4365</v>
+        <v>2059</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15353,10 +15353,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685200</v>
+        <v>685163</v>
       </c>
       <c r="R140" t="n">
-        <v>7315632</v>
+        <v>7315675</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY143"/>
+  <dimension ref="A1:AZ143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640604</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640788</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118642378</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644454</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888900</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649362</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644455</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1477,6 +1517,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649359</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1578,6 +1623,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640602</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1679,6 +1729,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644451</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1780,6 +1835,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640784</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1877,6 +1937,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649337</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1982,6 +2047,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113078297</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2087,6 +2157,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767973</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2184,6 +2259,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649361</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2289,6 +2369,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767650</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2394,6 +2479,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113078256</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2499,6 +2589,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767749</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2604,6 +2699,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767797</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2709,6 +2809,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767979</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2806,6 +2911,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649336</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2911,6 +3021,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767724</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3016,6 +3131,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767773</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3122,6 +3242,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888904</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3223,6 +3348,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640432</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3324,6 +3454,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640781</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3425,6 +3560,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644449</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3530,6 +3670,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767758</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3627,6 +3772,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649355</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3733,6 +3883,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183859</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3838,6 +3993,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767599</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3935,6 +4095,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649370</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4041,6 +4206,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888903</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4146,6 +4316,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767627</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4251,6 +4426,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767690</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4348,6 +4528,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649363</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4445,6 +4630,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649364</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4542,6 +4732,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649365</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4639,6 +4834,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649366</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4744,6 +4944,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113078260</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4845,6 +5050,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640438</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4946,6 +5156,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640440</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5047,6 +5262,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640606</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5148,6 +5368,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640607</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5249,6 +5474,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640608</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5350,6 +5580,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640609</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5451,6 +5686,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640790</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5552,6 +5792,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640791</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5653,6 +5898,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640792</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5754,6 +6004,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118642382</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5855,6 +6110,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118642383</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5956,6 +6216,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644456</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6057,6 +6322,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118661409</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6158,6 +6428,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118661410</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6263,6 +6538,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767811</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6368,6 +6648,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767952</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6474,6 +6759,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183690</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6575,6 +6865,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649344</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6681,6 +6976,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888901</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6782,6 +7082,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640778</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6883,6 +7188,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644448</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6988,6 +7298,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767965</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7093,6 +7408,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767888</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7190,6 +7510,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649360</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7295,6 +7620,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113078233</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7396,6 +7726,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640437</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7497,6 +7832,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644453</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7594,6 +7934,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649347</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7691,6 +8036,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649348</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7788,6 +8138,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649349</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7885,6 +8240,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649350</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7982,6 +8342,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649351</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8079,6 +8444,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649352</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8180,6 +8550,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640612</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8281,6 +8656,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644458</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8378,6 +8758,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649319</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8479,6 +8864,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640588</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8580,6 +8970,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644440</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8681,6 +9076,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640601</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8783,6 +9183,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640785</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8884,6 +9289,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644450</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8981,6 +9391,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649321</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9078,6 +9493,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649322</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9175,6 +9595,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649323</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9272,6 +9697,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649324</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9369,6 +9799,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649325</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9466,6 +9901,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649326</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9563,6 +10003,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649327</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9664,6 +10109,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640430</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9765,6 +10215,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640590</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9866,6 +10321,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640591</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9967,6 +10427,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640592</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10068,6 +10533,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640773</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10169,6 +10639,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640774</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10270,6 +10745,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644443</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10367,6 +10847,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649353</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10464,6 +10949,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649354</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10561,6 +11051,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649367</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10658,6 +11153,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649368</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10755,6 +11255,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649369</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10856,6 +11361,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640610</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10957,6 +11467,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640611</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11058,6 +11573,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118642384</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11159,6 +11679,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118642386</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11260,6 +11785,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644457</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11357,6 +11887,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649341</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11454,6 +11989,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649342</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11556,6 +12096,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649343</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11666,6 +12211,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111768033</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11776,6 +12326,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113078271</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11888,6 +12443,11 @@
       <c r="AY112" t="inlineStr">
         <is>
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644445</t>
         </is>
       </c>
     </row>
@@ -11998,6 +12558,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767946</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12107,6 +12672,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117381726</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12208,6 +12778,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767961</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12310,6 +12885,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649357</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12412,6 +12992,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649358</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12509,6 +13094,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649345</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12606,6 +13196,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649346</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12708,6 +13303,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117381608</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12810,6 +13410,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117381618</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12911,6 +13516,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649356</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13010,6 +13620,11 @@
       <c r="AY123" t="inlineStr">
         <is>
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640600</t>
         </is>
       </c>
     </row>
@@ -13117,6 +13732,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640783</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13218,6 +13838,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118642377</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13315,6 +13940,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649328</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13412,6 +14042,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649329</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13509,6 +14144,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649330</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13606,6 +14246,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649331</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13703,6 +14348,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649332</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13800,6 +14450,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649333</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13897,6 +14552,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649334</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13998,6 +14658,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640594</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14099,6 +14764,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640595</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14200,6 +14870,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640775</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14301,6 +14976,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640776</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14402,6 +15082,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118642374</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14503,6 +15188,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644444</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14608,6 +15298,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767869</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14705,6 +15400,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649338</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14810,6 +15510,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767613</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14915,6 +15620,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767593</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15025,8 +15735,157 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114799897</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>